--- a/astro-site/public/dl/guia-restaurante-nikkei/plan-financiero-3-anos.xlsx
+++ b/astro-site/public/dl/guia-restaurante-nikkei/plan-financiero-3-anos.xlsx
@@ -11,7 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inversión" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inversión'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'P&amp;L Mensual'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -519,9 +522,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -541,6 +544,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -583,10 +587,19 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-nikkei · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -595,7 +608,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -604,7 +626,7 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -631,6 +653,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -680,7 +703,7 @@
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="10">
         <f>D5-C5</f>
-        <v/>
+        <v>-110000.0</v>
       </c>
       <c r="F5" s="11" t="n"/>
     </row>
@@ -701,7 +724,7 @@
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="10">
         <f>D6-C6</f>
-        <v/>
+        <v>-14000.0</v>
       </c>
       <c r="F6" s="11" t="n"/>
     </row>
@@ -722,7 +745,7 @@
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="10">
         <f>D7-C7</f>
-        <v/>
+        <v>-9000.0</v>
       </c>
       <c r="F7" s="11" t="n"/>
     </row>
@@ -743,7 +766,7 @@
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="10">
         <f>D8-C8</f>
-        <v/>
+        <v>-10000.0</v>
       </c>
       <c r="F8" s="11" t="n"/>
     </row>
@@ -764,7 +787,7 @@
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="10">
         <f>D9-C9</f>
-        <v/>
+        <v>-12000.0</v>
       </c>
       <c r="F9" s="11" t="n"/>
     </row>
@@ -785,7 +808,7 @@
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="10">
         <f>D10-C10</f>
-        <v/>
+        <v>-3200.0</v>
       </c>
       <c r="F10" s="11" t="n"/>
     </row>
@@ -806,7 +829,7 @@
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="10">
         <f>D11-C11</f>
-        <v/>
+        <v>-6500.0</v>
       </c>
       <c r="F11" s="11" t="n"/>
     </row>
@@ -827,7 +850,7 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="10">
         <f>D12-C12</f>
-        <v/>
+        <v>-2800.0</v>
       </c>
       <c r="F12" s="11" t="n"/>
     </row>
@@ -848,7 +871,7 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="10">
         <f>D13-C13</f>
-        <v/>
+        <v>-600.0</v>
       </c>
       <c r="F13" s="11" t="n"/>
     </row>
@@ -869,7 +892,7 @@
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="10">
         <f>D14-C14</f>
-        <v/>
+        <v>-8500.0</v>
       </c>
       <c r="F14" s="11" t="n"/>
     </row>
@@ -890,7 +913,7 @@
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10">
         <f>D15-C15</f>
-        <v/>
+        <v>-4500.0</v>
       </c>
       <c r="F15" s="11" t="n"/>
     </row>
@@ -911,7 +934,7 @@
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="10">
         <f>D16-C16</f>
-        <v/>
+        <v>-2800.0</v>
       </c>
       <c r="F16" s="11" t="n"/>
     </row>
@@ -932,7 +955,7 @@
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="10">
         <f>D17-C17</f>
-        <v/>
+        <v>-5500.0</v>
       </c>
       <c r="F17" s="11" t="n"/>
     </row>
@@ -953,7 +976,7 @@
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="10">
         <f>D18-C18</f>
-        <v/>
+        <v>-1200.0</v>
       </c>
       <c r="F18" s="11" t="n"/>
     </row>
@@ -974,7 +997,7 @@
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="10">
         <f>D19-C19</f>
-        <v/>
+        <v>-12000.0</v>
       </c>
       <c r="F19" s="11" t="n"/>
     </row>
@@ -995,7 +1018,7 @@
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="10">
         <f>D20-C20</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="F20" s="11" t="n"/>
     </row>
@@ -1016,7 +1039,7 @@
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="10">
         <f>D21-C21</f>
-        <v/>
+        <v>-2500.0</v>
       </c>
       <c r="F21" s="11" t="n"/>
     </row>
@@ -1037,7 +1060,7 @@
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="10">
         <f>D22-C22</f>
-        <v/>
+        <v>-2500.0</v>
       </c>
       <c r="F22" s="11" t="n"/>
     </row>
@@ -1058,7 +1081,7 @@
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="10">
         <f>D23-C23</f>
-        <v/>
+        <v>-6000.0</v>
       </c>
       <c r="F23" s="11" t="n"/>
     </row>
@@ -1079,7 +1102,7 @@
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="10">
         <f>D24-C24</f>
-        <v/>
+        <v>-4500.0</v>
       </c>
       <c r="F24" s="11" t="n"/>
     </row>
@@ -1100,7 +1123,7 @@
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="10">
         <f>D25-C25</f>
-        <v/>
+        <v>-5500.0</v>
       </c>
       <c r="F25" s="11" t="n"/>
     </row>
@@ -1121,7 +1144,7 @@
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="10">
         <f>D26-C26</f>
-        <v/>
+        <v>-10000.0</v>
       </c>
       <c r="F26" s="11" t="n"/>
     </row>
@@ -1142,7 +1165,7 @@
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="10">
         <f>D27-C27</f>
-        <v/>
+        <v>-3500.0</v>
       </c>
       <c r="F27" s="11" t="n"/>
     </row>
@@ -1163,7 +1186,7 @@
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="10">
         <f>D28-C28</f>
-        <v/>
+        <v>-9000.0</v>
       </c>
       <c r="F28" s="11" t="n"/>
     </row>
@@ -1184,7 +1207,7 @@
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="10">
         <f>D29-C29</f>
-        <v/>
+        <v>-4500.0</v>
       </c>
       <c r="F29" s="11" t="n"/>
     </row>
@@ -1205,7 +1228,7 @@
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="10">
         <f>D30-C30</f>
-        <v/>
+        <v>-900.0</v>
       </c>
       <c r="F30" s="11" t="n"/>
     </row>
@@ -1226,7 +1249,7 @@
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="10">
         <f>D31-C31</f>
-        <v/>
+        <v>-12000.0</v>
       </c>
       <c r="F31" s="11" t="n"/>
     </row>
@@ -1247,7 +1270,7 @@
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="10">
         <f>D32-C32</f>
-        <v/>
+        <v>-1800.0</v>
       </c>
       <c r="F32" s="11" t="n"/>
     </row>
@@ -1268,7 +1291,7 @@
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="10">
         <f>D33-C33</f>
-        <v/>
+        <v>-22000.0</v>
       </c>
       <c r="F33" s="11" t="n"/>
     </row>
@@ -1289,7 +1312,7 @@
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="10">
         <f>D34-C34</f>
-        <v/>
+        <v>-4000.0</v>
       </c>
       <c r="F34" s="11" t="n"/>
     </row>
@@ -1310,7 +1333,7 @@
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="10">
         <f>D35-C35</f>
-        <v/>
+        <v>-8000.0</v>
       </c>
       <c r="F35" s="11" t="n"/>
     </row>
@@ -1331,7 +1354,7 @@
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="10">
         <f>D36-C36</f>
-        <v/>
+        <v>-800.0</v>
       </c>
       <c r="F36" s="11" t="n"/>
     </row>
@@ -1352,7 +1375,7 @@
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="10">
         <f>D37-C37</f>
-        <v/>
+        <v>-3500.0</v>
       </c>
       <c r="F37" s="11" t="n"/>
     </row>
@@ -1373,7 +1396,7 @@
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="10">
         <f>D38-C38</f>
-        <v/>
+        <v>-2500.0</v>
       </c>
       <c r="F38" s="11" t="n"/>
     </row>
@@ -1394,7 +1417,7 @@
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="10">
         <f>D39-C39</f>
-        <v/>
+        <v>-4500.0</v>
       </c>
       <c r="F39" s="11" t="n"/>
     </row>
@@ -1415,7 +1438,7 @@
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="10">
         <f>D40-C40</f>
-        <v/>
+        <v>-1200.0</v>
       </c>
       <c r="F40" s="11" t="n"/>
     </row>
@@ -1436,7 +1459,7 @@
       <c r="D41" s="9" t="n"/>
       <c r="E41" s="10">
         <f>D41-C41</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="F41" s="11" t="n"/>
     </row>
@@ -1457,7 +1480,7 @@
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="10">
         <f>D42-C42</f>
-        <v/>
+        <v>-3500.0</v>
       </c>
       <c r="F42" s="11" t="n"/>
     </row>
@@ -1478,7 +1501,7 @@
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="10">
         <f>D43-C43</f>
-        <v/>
+        <v>-3500.0</v>
       </c>
       <c r="F43" s="11" t="n"/>
     </row>
@@ -1499,7 +1522,7 @@
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="10">
         <f>D44-C44</f>
-        <v/>
+        <v>-12000.0</v>
       </c>
       <c r="F44" s="11" t="n"/>
     </row>
@@ -1520,7 +1543,7 @@
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="10">
         <f>D45-C45</f>
-        <v/>
+        <v>-500.0</v>
       </c>
       <c r="F45" s="11" t="n"/>
     </row>
@@ -1541,7 +1564,7 @@
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="10">
         <f>D46-C46</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="F46" s="11" t="n"/>
     </row>
@@ -1562,7 +1585,7 @@
       <c r="D47" s="9" t="n"/>
       <c r="E47" s="10">
         <f>D47-C47</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="F47" s="11" t="n"/>
     </row>
@@ -1583,7 +1606,7 @@
       <c r="D48" s="9" t="n"/>
       <c r="E48" s="10">
         <f>D48-C48</f>
-        <v/>
+        <v>-15000.0</v>
       </c>
       <c r="F48" s="11" t="n"/>
     </row>
@@ -1604,7 +1627,7 @@
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="10">
         <f>D49-C49</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="F49" s="11" t="n"/>
     </row>
@@ -1625,10 +1648,11 @@
       <c r="D50" s="9" t="n"/>
       <c r="E50" s="10">
         <f>D50-C50</f>
-        <v/>
+        <v>-70000.0</v>
       </c>
       <c r="F50" s="11" t="n"/>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="B52" s="12" t="inlineStr">
         <is>
@@ -1637,17 +1661,18 @@
       </c>
       <c r="C52" s="13">
         <f>SUM(C5:C50)</f>
-        <v/>
+        <v>441300.0</v>
       </c>
       <c r="D52" s="13">
         <f>SUM(D5:D50)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E52" s="13">
         <f>D52-C52</f>
-        <v/>
-      </c>
-    </row>
+        <v>-441300.0</v>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
@@ -1657,11 +1682,20 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1670,7 +1704,7 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1705,6 +1739,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1828,7 +1863,7 @@
       </c>
       <c r="N6" s="13">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>540000.0</v>
       </c>
     </row>
     <row r="7">
@@ -1875,7 +1910,7 @@
       </c>
       <c r="N7" s="13">
         <f>SUM(B7:M7)</f>
-        <v/>
+        <v>180000.0</v>
       </c>
     </row>
     <row r="8">
@@ -1922,7 +1957,7 @@
       </c>
       <c r="N8" s="13">
         <f>SUM(B8:M8)</f>
-        <v/>
+        <v>120000.0</v>
       </c>
     </row>
     <row r="9">
@@ -1969,7 +2004,7 @@
       </c>
       <c r="N9" s="13">
         <f>SUM(B9:M9)</f>
-        <v/>
+        <v>96000.0</v>
       </c>
     </row>
     <row r="10">
@@ -2040,7 +2075,7 @@
       </c>
       <c r="N14" s="13">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>8400.0</v>
       </c>
     </row>
     <row r="15">
@@ -2104,7 +2139,7 @@
       </c>
       <c r="N18" s="13">
         <f>SUM(B18:M18)</f>
-        <v/>
+        <v>78000.0</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2186,7 @@
       </c>
       <c r="N19" s="13">
         <f>SUM(B19:M19)</f>
-        <v/>
+        <v>264000.0</v>
       </c>
     </row>
     <row r="20">
@@ -2198,7 +2233,7 @@
       </c>
       <c r="N20" s="13">
         <f>SUM(B20:M20)</f>
-        <v/>
+        <v>156000.0</v>
       </c>
     </row>
     <row r="21">
@@ -2245,7 +2280,7 @@
       </c>
       <c r="N21" s="13">
         <f>SUM(B21:M21)</f>
-        <v/>
+        <v>42000.0</v>
       </c>
     </row>
     <row r="22">
@@ -2292,7 +2327,7 @@
       </c>
       <c r="N22" s="13">
         <f>SUM(B22:M22)</f>
-        <v/>
+        <v>6000.0</v>
       </c>
     </row>
     <row r="23">
@@ -2339,7 +2374,7 @@
       </c>
       <c r="N23" s="13">
         <f>SUM(B23:M23)</f>
-        <v/>
+        <v>6000.0</v>
       </c>
     </row>
     <row r="24">
@@ -2386,7 +2421,7 @@
       </c>
       <c r="N24" s="13">
         <f>SUM(B24:M24)</f>
-        <v/>
+        <v>14400.0</v>
       </c>
     </row>
     <row r="25">
@@ -2433,7 +2468,7 @@
       </c>
       <c r="N25" s="13">
         <f>SUM(B25:M25)</f>
-        <v/>
+        <v>5400.0</v>
       </c>
     </row>
     <row r="26">
@@ -2480,7 +2515,7 @@
       </c>
       <c r="N26" s="13">
         <f>SUM(B26:M26)</f>
-        <v/>
+        <v>4800.0</v>
       </c>
     </row>
     <row r="27">
@@ -2527,7 +2562,7 @@
       </c>
       <c r="N27" s="13">
         <f>SUM(B27:M27)</f>
-        <v/>
+        <v>21600.0</v>
       </c>
     </row>
     <row r="28">
@@ -2574,7 +2609,7 @@
       </c>
       <c r="N28" s="13">
         <f>SUM(B28:M28)</f>
-        <v/>
+        <v>8400.0</v>
       </c>
     </row>
     <row r="29">
@@ -2601,6 +2636,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -2614,6 +2650,15 @@
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A34:N34"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>